--- a/altium-library.xlsx
+++ b/altium-library.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffr\OneDrive\Documents\GitHub\altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD6571-26C5-4B28-8260-2D8CB979E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E170D-A43E-4F53-B139-DD5C04BF1C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{7DEBF9EA-A0BE-4638-876A-B381D67440C7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{7DEBF9EA-A0BE-4638-876A-B381D67440C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors" sheetId="1" r:id="rId1"/>
+    <sheet name="Resistors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>CAP</t>
   </si>
@@ -72,6 +73,21 @@
   </si>
   <si>
     <t>Symbol Ref</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>General purpose resistor</t>
+  </si>
+  <si>
+    <t>Generic 0402 resistor</t>
   </si>
 </sst>
 </file>
@@ -495,4 +511,54 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DAC21E-7E8E-4A02-8828-D0AEAE2C7BAC}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.53125" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>